--- a/候选事故案例简短分析.xlsx
+++ b/候选事故案例简短分析.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="候选案例简短分析" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="景元卡池支付事故·深入分析" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -35,6 +36,10 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="002E75B6"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00C00000"/>
     </font>
     <font>
@@ -47,7 +52,18 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="007030A0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00BF8F00"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -89,7 +105,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -111,6 +127,22 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -477,23 +509,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H15"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
-    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="55" customWidth="1" min="6" max="6"/>
-    <col width="55" customWidth="1" min="7" max="7"/>
-    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="7" customWidth="1" min="5" max="5"/>
+    <col width="48" customWidth="1" min="6" max="6"/>
+    <col width="48" customWidth="1" min="7" max="7"/>
+    <col width="48" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1" ht="40" customHeight="1">
+    <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>分析框架沿用经典案例：① 事件发生链路与直接影响 → ② 造成影响的根因推测与玩家侧原因 → ③ 后续落地情况与版本运营启示。按时间逻辑分析整个事件的处理，把原因说清楚或按完整逻辑推测清楚；运营基本原则：积极响应、历史一致、玩家有利（从玩家视角出发）。</t>
+          <t>框架沿用经典案例三段式：①事件链路与影响 → ②根因推测与玩家侧原因 → ③运营启示。事件类型区分：技术事故（版本运营主责）／舆情危机（建议移交玩家运营深入分析，版本运营切入点在内审）／内控泄密（按对项目的影响定级）。</t>
         </is>
       </c>
     </row>
@@ -515,31 +548,36 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
+          <t>事件类型</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
           <t>严重性</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>① 事件发生链路与直接影响</t>
-        </is>
-      </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>② 造成影响的根因推测与玩家侧原因</t>
+          <t>① 事件链路与直接影响</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>③ 后续落地情况与版本运营启示</t>
+          <t>② 根因推测与玩家侧原因</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>③ 运营启示</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
           <t>主要参考资料</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="400" customHeight="1">
+    <row r="3" ht="210" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
           <t>CB前</t>
@@ -552,51 +590,46 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>国服崩铁官网及社区预约接口无法预约</t>
+          <t>官网及米游社预约接口无法预约</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
-        <is>
-          <t>1. 首曝节点：预约成为玩家与游戏的第一触点
-2021年10月《崩坏：星穹铁道》首曝并开启首测招募，官网与米游社预约页是玩家表达兴趣、争取测试资格的唯一入口。首曝PV带来的流量在极短时间内集中涌入。
-2. 异常表现：预约接口无法提交，页面加载失败
-大量玩家反馈官网打不开、米游社预约接口无法完成预约。对玩家来说，直接感知是“想报名但报不上”，且无法判断是自己网络问题、名额已满，还是系统故障。
-3. 玩家感知与直接影响
-预约与测试资格、预约奖励预期直接绑定，接口异常立即引发“会不会错过资格”的焦虑。作为新IP的第一次公开亮相，第一触点的体验受损会直接消耗首曝热度带来的情绪窗口。</t>
-        </is>
-      </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：首曝流量峰值远超预约链路容量预估
-预约链路涉及官网页面、米游社接口、账号验证等多个环节，任何一环容量不足都会形成阻塞。首曝属于一次性、不可复现的流量事件，峰值很难用日常数据预估，压测和弹性扩容准备不足时最容易在这里出问题。
-2. 关键处理缺口：缺少排队、降级与预期管理手段
-高峰期没有排队页或静态兜底页承接玩家，玩家只能反复刷新，进一步加剧拥堵，也放大了“报不上名”的焦虑。
-3. 玩家侧原因：资格稀缺感放大了拥堵体验
-测试资格天然稀缺，玩家会默认“先到先得”，因此接口异常被理解成机会损失而不是普通故障。</t>
+          <t>1. 2021年10月首曝并开启首测招募，流量短时集中涌入，官网打不开、米游社预约接口无法提交。
+2. 玩家无法判断是网络问题、名额已满还是系统故障，担心错过测试资格。
+3. 预约页是新IP的第一触点，接口异常直接消耗首曝热度。</t>
         </is>
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-预约功能随扩容恢复，首曝热度未受根本影响，游戏最终以千万级预约进入公测。但该事件说明预热类基础设施与正式服同样是“线上服务”。
-2. 运营启示
-第一，首曝、预约、周年庆等一次性流量事件要按峰值设计并提前压测，准备排队页、静态降级页等兜底方案。
-第二，异常发生时要第一时间公告“资格不会因拥堵丢失”，切断稀缺焦虑的放大链路。
-第三，预约类页面的可用性直接等于品牌第一印象，应纳入版本级发布检查而非当作普通宣传页。</t>
+          <t>1. 根因推断：首曝属一次性流量事件，峰值难以用日常数据预估，预约链路（页面、接口、账号验证）容量不足。
+2. 处理缺口：高峰期无排队页或静态兜底，玩家反复刷新加剧拥堵。
+3. 玩家侧：测试资格稀缺、默认先到先得，拥堵被理解为机会损失。</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
         <is>
-          <t>米游社预约页 webstatic.mihoyo.com/rpg/event/e20211008reserve；游戏日报：预约人数破1000万报道 news.yxrb.net/2023/0131/1035.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="400" customHeight="1">
+          <t>1. 预约功能随扩容恢复，未影响后续千万级预约。
+2. 启示：首曝、预约、周年庆等一次性流量事件按峰值压测，备好排队页与降级方案；异常时先公告"资格不会因拥堵丢失"。</t>
+        </is>
+      </c>
+      <c r="I3" s="3" t="inlineStr">
+        <is>
+          <t>米游社预约页 webstatic.mihoyo.com/rpg/event/e20211008reserve；游戏日报 news.yxrb.net/2023/0131/1035.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="210" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>1.0</t>
@@ -609,53 +642,42 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>景元卡池开启时，玩家无法支付/充值延迟</t>
+          <t>景元卡池开启时充值延迟/无法到账</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>1. 卡池开启：支付订单量瞬时到达峰值
-2023年5月17日景元卡池开启。景元是公测后首个人气极高的限定五星，卡池开启瞬间大量玩家集中充值抽取。
-2. 异常表现：充值延迟20分钟以上甚至未到账
-玩家反馈支付完成后星琼迟迟不到账，部分订单超过20分钟仍未发货。TapTap、微博等平台出现集中反馈，“被氪爆”成为当日热议话题。
-3. 官方措施：当日响应并完成修复
-官方当日回应“已注意到充值到账延迟问题，正在修复中”，并于5月17日18:30左右完成修复；对未到账订单，玩家在原设备登录可自动补发，仍未到账可凭订单截图联系客服。随后向玩家发放120星琼补偿。
-4. 造成影响
-事故发生在付费核心链路上，玩家“钱已扣、货未到”的焦虑在卡池限时窗口内被最大化；但由于响应快、路径清晰、有补偿，事件没有升级为长期信任危机。</t>
-        </is>
-      </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：支付发货链路未按卡池峰值扩容
-新五星卡池开启瞬间的订单量远超日常水位，支付回调、发货队列在峰值下产生积压。公测初期缺少足够的历史数据来预估“人气角色卡池”这一量级。
-2. 关键处理缺口：峰值预案与玩家侧的即时安抚
-问题本身是容量问题，但玩家真正恐慌的是“钱会不会白花”。在修复完成前，最需要的是一句明确的“已支付订单不会丢失、会自动补发”。
-3. 玩家侧原因：付费链路异常触发最强焦虑
-卡池限时+抽卡冲动窗口，让玩家对到账速度极其敏感；20分钟的延迟在其他场景可以接受，在“正在抽卡”的场景里等同于服务中断。</t>
+          <t>→ 已升级为深入分析，见「景元卡池支付事故·深入分析」Sheet。
+补齐登录支付核心链路选题，也是1.x期间实际发放线上补偿（星琼×120）的事故样本。</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-修复+自动补发+120星琼补偿形成了完整闭环，事件当日收束。此后大型卡池节点的支付稳定性成为版本保障的常规项。
-2. 运营启示
-第一，卡池开启、周年庆等付费峰值节点，支付与发货链路要提前扩容并做峰值演练。
-第二，支付类事故的公告要先回答玩家最关心的问题：已支付的订单是否安全、何时到账、找谁处理，技术原因可以后置。
-第三，“快速修复+自动补发+小额普发补偿”是付费类事故的标准处理范式，符合积极响应、玩家有利的原则。</t>
+          <t>（见深入分析Sheet）</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>游民星空：景元上线氪爆服务器 gamersky.com/news/202305/1598070.shtml；每经网/腾讯新闻：官方回应充值到账延迟 nbd.com.cn/articles/2023-05-17/2829739.html；TapTap修复说明 taptap.cn/moment/408008642420281110</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="400" customHeight="1">
+          <t>（见深入分析Sheet）</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>游民星空 gamersky.com/news/202305/1598070.shtml；每经网 nbd.com.cn/articles/2023-05-17/2829739.html；TapTap修复说明 taptap.cn/moment/408008642420281110</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="210" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
           <t>1.1</t>
@@ -668,53 +690,46 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>博物馆活动设计问题：主线做完无法获取经营进度奖励</t>
-        </is>
-      </c>
-      <c r="D5" s="5" t="inlineStr">
+          <t>博物馆主线完成后无法获取经营进度奖励</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t>1. 活动上线：剧情任务与经营玩法双模块绑定
-「冬城博物珍奇簿」是1.1版本的大型限时活动，包含【博物馆经营】与【展品和助手收集】两个模块，玩家完成活动主线后通过持续经营推进阶段、领取限时奖励。
-2. 异常表现：主线完成后经营进度奖励无法正常获取
-部分玩家完成博物馆主线后，经营进度奖励无法领取或进度推进受阻，限时奖励（含星琼等）面临错过风险。
-3. 玩家感知：限时奖励错过焦虑
-活动奖励与限时窗口绑定，玩家的核心疑问是“我还能不能拿全奖励”，并转向社区搜索确认是bug还是自己漏做了前置。
-4. 官方措施：延长领取时间并补偿
-官方将限时奖励领取截止延长至2023年8月7日，达成「光辉巅峰」后仍可继续经营完成任务领取奖励，并对体验影响发放补偿。</t>
-        </is>
-      </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：多模块活动的状态依赖判定不同步
-活动把剧情任务完成状态、经营阶段解锁、奖励领取条件串在一条链路上，主线完成标记与经营进度判定之间的同步一旦异常，玩家侧就表现为“做完了却拿不到”。
-2. 关键处理缺口：多层解锁链路的上线前校验
-这类“任务→玩法→奖励”多层绑定的活动，需要针对不同完成顺序、不同进度组合做覆盖测试，单独测每个模块无法暴露组合状态问题。
-3. 玩家侧原因：限时性放大了阻塞感
-玩家不怕奖励晚到，怕的是错过。限时活动中任何奖励链路阻塞都会被按“损失”而非“延迟”来感知。</t>
+          <t>1. 「冬城博物珍奇簿」含经营与收集双模块，部分玩家完成主线后经营进度奖励无法领取。
+2. 奖励与限时窗口绑定，玩家核心疑问是"还能不能拿全奖励"。
+3. 官方将限时奖励领取延长至8月7日，并发放补偿。</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-延长领取时间+补偿的处理让玩家实际损失归零，事件平稳收束，是“玩家有利”原则的正面示范：处理方案直接消除了限时焦虑的根源。
-2. 运营启示
-第一，大型活动的任务、玩法、奖励多层解锁要按完整链路和多种完成顺序做组合测试。
-第二，限时奖励类问题的最优解是“延长窗口”，它比单纯补偿更能对症——玩家要的是拿到奖励的确定性。
-第三，早期版本活动结构相对简单尚且出现状态同步问题，后续联动、周年等更复杂活动（如3.4联动圣杯事件）更需要把“完成状态→解锁状态”的校验作为标准测试项。</t>
+          <t>1. 根因推断：主线完成标记与经营进度判定不同步，"任务→玩法→奖励"多层解锁链路中某环状态异常。
+2. 处理缺口：多模块活动缺少不同完成顺序的组合测试。
+3. 玩家侧：限时奖励阻塞被按损失感知，而非延迟。</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>GameKee：冬城博物珍奇簿限时奖励获取延长补偿 gamekee.com/xqtd/614470.html；知乎：如何评价1.1版本活动冬城博物珍奇簿 zhihu.com/question/605662846</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="400" customHeight="1">
+          <t>1. "延长窗口+补偿"让玩家实际损失归零，处理对症，是玩家有利原则的正面样本。
+2. 启示：多层解锁活动按完整链路和多种完成顺序测试；限时奖励类问题优先延长窗口，比单纯补偿更能消除焦虑。</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>GameKee补偿公告 gamekee.com/xqtd/614470.html；知乎 zhihu.com/question/605662846</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="210" customHeight="1">
       <c r="A6" s="3" t="inlineStr">
         <is>
           <t>2.3</t>
@@ -730,48 +745,43 @@
           <t>GeForce NOW云游戏平台更新异常</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
+        <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
-        <is>
-          <t>1. 版更节点：第三方云平台同步更新
-崩铁上线GeForce NOW（台湾大哥大等区域运营）后，云平台玩家依赖平台侧部署的客户端镜像游玩。2.3版本更新时，平台侧出现更新异常。
-2. 异常表现：云平台玩家无法进入新版本
-GFN玩家在版更后无法正常启动或更新游戏，官方/平台侧发布“GeForce NOW云端游戏平台更新异常问题”说明，玩家需等待平台完成部署。
-3. 玩家感知与直接影响
-受影响的是依赖云游戏的玩家群体——多为本地设备性能受限、没有替代登录手段的用户，对他们而言版本首日完全无法游玩。影响范围小（单一平台、单一区域），但受影响个体的阻塞是完全的。</t>
-        </is>
-      </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：第三方部署节奏与版更包发布存在时间差
-云游戏平台的客户端更新由平台方部署，游戏侧版更包上线与平台侧镜像同步之间存在依赖。同步流程失败或滞后，就会出现“正式服已更新、云平台进不去”的断层。
-2. 关键处理缺口：第三方渠道的版更协同与验证
-版更验证通常聚焦自有渠道（官服、主要应用商店），云游戏等第三方平台容易成为检查盲区，出问题后责任和恢复时间也依赖对方。
-3. 玩家侧原因：无替代路径的完全阻塞
-云平台玩家无法像PC/手机玩家那样换设备自救，因此虽然事件整体量级小，个体体验上等同于停服。</t>
+          <t>1. 2.3版更后，GFN平台（台湾大哥大等运营）客户端镜像更新异常，云平台玩家无法进入新版本。
+2. 官方与平台侧发布异常说明，玩家等待平台完成部署后恢复。
+3. 受影响群体多为设备受限、无替代登录手段的用户，个体阻塞完全。</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-平台完成部署后恢复，事件影响时间有限，未形成大范围舆情。
-2. 运营启示
-第一，云游戏、渠道服等第三方平台要纳入版本发布检查单，明确双方的同步时间点、验证责任和回滚方案。
-第二，第三方侧异常时，游戏官方与平台方应同时发布公告并给出恢复预期，避免玩家在两边客服之间来回踢皮球。
-第三，评估此类事故严重性时要注意“平均影响小、个体阻塞完全”的结构，对受影响群体的补偿和解释不应因为总量小而降级。</t>
+          <t>1. 根因推断：云平台客户端由平台方部署，与版更包上线存在同步依赖，同步失败或滞后即出现断层。
+2. 处理缺口：版更验证聚焦自有渠道，第三方云平台是检查盲区，恢复时间受制于对方。
+3. 玩家侧：无法换设备自救，版本首日完全无法游玩。</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t>台湾大哥大GFN官方页 gfn.taiwanmobile.com/portal/news/article/335；官方Facebook异常说明贴 facebook.com（崩壊：星穹鐵道 GeForce Now雲端遊戲平台更新異常問題）</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="400" customHeight="1">
+          <t>1. 平台完成部署后恢复，影响时间有限。
+2. 启示：云游戏、渠道服纳入版本发布检查单，明确双方同步时间点与验证责任；异常时双侧同时公告并给出恢复预期。事故总量小，但对受影响群体的解释与补偿不应降级。</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
+          <t>台湾大哥大GFN gfn.taiwanmobile.com/portal/news/article/335；官方Facebook异常说明贴</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="210" customHeight="1">
       <c r="A7" s="3" t="inlineStr">
         <is>
           <t>3.0</t>
@@ -789,48 +799,42 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
+          <t>舆情危机</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="E7" s="3" t="inlineStr">
-        <is>
-          <t>1. 活动上线：春节福利引入概率机制
-3.0春节期间「银河幸运星」活动让玩家每日在“稳定100星琼”与“50星琼+10%概率额外550星琼（极小概率50万星琼）”之间二选一。多数选择概率档的玩家连续多日未触发，实际收益明显低于稳定档。
-2. 舆情发酵：官方文案“愿赌服输”成为引爆点
-玩家对概率设计的不满累积之际，官方社媒互动中出现“愿赌服输”表述，被玩家普遍解读为官方贴脸嘲讽“赌输”的玩家。不满从活动机制转向官方态度，微博、B站评论区迅速升温。
-3. 事件升级：从活动争议升级为态度危机
-有玩家计算连续七天全部只拿50星琼的概率达47.8%，“春节福利变赌桌”的叙事扩散；讨论重点从“奖励少了多少”变成“官方是否在嘲讽玩家”，社区开始集中索要补偿。
-4. 造成影响
-事件发生在春节这一情绪高点，福利预期与实际体验的落差被文案二次放大，成为3.X开局阶段官方与玩家关系恶化的标志性事件之一。</t>
-        </is>
-      </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：活动机制与运营文案同时出问题
-机制层面，节日福利用“赌”包装，负反馈天然集中在未中奖的多数玩家身上；文案层面，官方帐号在玩家已有不满时使用对抗性表述，等于亲手把机制争议升级为态度争议。两个问题单独出现都可控，叠加在春节节点上导致情绪窗口完全失效。
-2. 关键处理缺口：官方帐号文案缺少舆情敏感性审查
-社媒运营与版本运营的口径没有拉通。在活动负反馈已经可见的情况下，任何玩梗式表述都应先过一道“会不会被读成嘲讽”的审查。
-3. 玩家侧原因：春节福利的普惠预期被违背
-玩家默认节日福利是普惠性质的“过年红包”，概率设计让相当比例玩家实际拿得更少；官方文案又否定了这种不满的正当性，“我亏了还被嘲笑”是比“我亏了”强烈得多的情绪。</t>
+          <t>1. 春节活动让玩家每日在"稳定100星琼"与"50+10%概率550"间二选一，多数选概率档的玩家连续未中，收益低于稳定档，不满累积。
+2. 官方社媒互动中出现"愿赌服输"表述，被解读为嘲讽玩家，微博、B站评论区迅速升温。
+3. 有玩家算出七天全拿50星琼的概率达47.8%，"春节福利变赌桌"叙事扩散，社区集中索要补偿。</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-官方后续通过3.0版本体验优化、老角色加强等动作缓和玩家关系，但“愿赌服输”成为社区长期记忆点，此后官方文案风格明显趋于谨慎。
-2. 运营启示
-第一，节日福利慎用概率机制，若使用必须有保底兜底，确保最差情况不低于玩家的普惠预期。
-第二，官方帐号的每一条互动都是运营口径，情绪升温期要冻结玩梗类表述，社媒、客服、公告口径统一。
-第三，节点情绪窗口（春节、周年）既是拉好感的机会也是放大器，同样的失误在平时是小事，在节点上会被数倍放大。</t>
+          <t>1. 根因推断：活动方案与运营文案两道内审同时失守——概率机制让多数玩家实拿低于普惠预期，文案又在负反馈可见时使用对抗性表述，把机制争议升级为态度争议。
+2. 玩家侧：春节福利被默认为普惠红包；"亏了还被嘲讽"的情绪强度远高于"亏了"。</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t>守塔资讯：春节幸运星活动遭大量玩家吐槽 m.shouta.cn/news/202502161215.html；TapTap讨论 taptap.cn/moment/635547474836062778；网易云游戏：愿赌服输背后的乌龙 cg.163.com/static/content/67a3161bd28806a79331b260</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="400" customHeight="1">
+          <t>【建议移交玩家运营深入分析；版本运营切入点在内审】
+1. 活动方案内审：节日福利慎用概率机制，用则必须有保底，最差情况不低于普惠预期。
+2. 文案内审：官方帐号每条互动都是运营口径，活动负反馈出现后冻结玩梗类表述，社媒、客服、公告口径拉通。
+3. 春节、周年等节点是情绪放大器，同等失误在节点上后果翻倍，节点期方案审查标准应上调。</t>
+        </is>
+      </c>
+      <c r="I7" s="3" t="inlineStr">
+        <is>
+          <t>守塔 m.shouta.cn/news/202502161215.html；TapTap taptap.cn/moment/635547474836062778；网易云游戏 cg.163.com/static/content/67a3161bd28806a79331b260</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="210" customHeight="1">
       <c r="A8" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
@@ -848,48 +852,42 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>1. 外部故障：海外云基础设施大规模异常
-2025年6月海外主要云服务商发生大规模故障，大量依赖其基础设施的互联网服务同时异常。崩铁海外服的支付/充值链路依赖第三方支付渠道与云服务，在故障期间受到传导影响。
-2. 异常表现：海外玩家支付失败或无法拉起支付
-故障期间海外玩家充值失败、支付页面无法拉起或订单状态异常。问题不在游戏自身代码，但玩家侧的直接感知就是“充不了值”。
-3. 玩家感知：无法区分“游戏坏了”还是“世界坏了”
-玩家第一反应是游戏支付系统故障，尤其正值卡池期的玩家会立即担心错过抽取窗口。在官方明确归因之前，客诉和社区求助会全部涌向游戏侧。
-4. 造成影响
-支付属于核心付费链路，故障期间等同于商业化服务中断；影响随云服务商恢复而消退，但暴露了单一外部依赖的脆弱性。</t>
-        </is>
-      </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：支付链路对外部云服务的单点依赖
-海外支付涉及支付渠道、账号服务、回调通知等多个环节，其中任何一环托管在故障云服务商上都会导致整条链路失效。这类风险不在游戏侧代码质量，而在架构上的依赖集中度。
-2. 关键处理缺口：外部故障的玩家侧归因与安抚
-外部依赖故障不是游戏的错，但响应义务仍在游戏侧。玩家最需要的是快速公告：问题来自第三方服务异常、已支付订单不会丢失、恢复后如何补发。缺少这层沟通，外部故障也会被记在游戏头上。
-3. 玩家侧原因：卡池期支付失败等同于抽卡受阻
-限时卡池让支付失败产生时间压力，玩家担心的不是“今天充不了”，而是“卡池结束前能不能充上”。</t>
+          <t>1. 2025年6月海外云服务商大规模故障，崩铁海外服支付链路受传导影响，玩家支付失败或无法拉起支付页。
+2. 玩家无法区分是游戏故障还是外部故障，客诉全部涌向游戏侧；卡池期玩家担心错过抽取窗口。
+3. 支付随云服务商修复恢复。</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-支付随云服务商故障修复而恢复。此类事件后，需要评估的是支付通道冗余和故障期间的应急预案，而非单点修复。
-2. 运营启示
-第一，外部依赖故障也要按线上事故标准响应：快速公告归因、明确订单安全、给出恢复预期，不能因为“不是我们的问题”就降低响应等级。
-第二，支付链路做多通道、多区域冗余，避免单一云服务商故障导致整条链路失效。
-第三，故障覆盖卡池窗口时，应评估卡池截止时间顺延或对受影响玩家的补偿方案，把外部故障对玩家抽取决策的影响降到最低——这是“玩家有利”原则在外部故障场景的落地。</t>
+          <t>1. 根因推断：支付渠道、账号服务、回调通知中有环节托管于故障云服务商，单点依赖导致整条链路失效。
+2. 处理缺口：外部故障的玩家侧归因与安抚——需要快速说明问题来自第三方、订单不会丢失、恢复后如何补发，否则账记在游戏头上。
+3. 玩家侧：限时卡池给支付失败加了时间压力。</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t>HoYoverse帮助中心支付错误专区 support.hoyoverse.com；HoYoLAB账号与支付系统维护公告 hoyolab.com/article/27519525（2025年6月外部云服务故障期间相关讨论以社区与新闻报道为主）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="400" customHeight="1">
+          <t>1. 启示：外部依赖故障按线上事故标准响应，快速公告归因、明确订单安全、给出恢复预期。
+2. 支付链路做多通道冗余，避免单一云服务商故障打穿全链路。
+3. 故障覆盖卡池窗口时，评估卡池顺延或对受影响玩家补偿。</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
+          <t>HoYoverse帮助中心 support.hoyoverse.com；HoYoLAB维护公告 hoyolab.com/article/27519525</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="210" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -905,50 +903,44 @@
           <t>遐蝶提前泄露，海外索赔15万美元</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>内控泄密</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="E9" s="3" t="inlineStr">
-        <is>
-          <t>1. 泄露发生：版本上线前的直播泄密
-3.2版本上线前不到一个月，海外玩家Alfredo Lopez在Discord直播展示未公开的遐蝶实机游玩内容，吸引超过12,000名观众。遐蝶是当期版本的重点输出角色，实机内容直接影响玩家的抽取预期形成。
-2. 法律行动：Cognosphere提起诉讼
-2025年6月6日，米哈游海外发行主体Cognosphere在美国加州中区联邦地区法院提起诉讼，以涉嫌违反版权法为由索赔15万美元。
-3. 舆情扩散：成为“米哈游打内鬼”系列的标志性案例
-事件被国内外媒体广泛报道。米哈游此前已在全球发起超过500件相关法律诉讼，本案因索赔金额明确、被告是普通玩家身份而引发讨论，社区出现同情被告与支持维权两种声音。
-4. 造成影响
-事件未阻断任何游戏服务，正式服运营不受影响。真正的影响在于：泄露内容提前锚定了玩家对角色的预期，官方前瞻、PV等宣发物料的信息价值被稀释；同时事件本身成为一次公共舆情。</t>
-        </is>
-      </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：测试内容分发链路存在泄露口
-未公开实机内容能被外部玩家直播，说明测试构建的分发范围（外部测试者、代理商、合作方）中存在管控失效的环节。泄露、内鬼问题的结果与运营受影响的严重程度并不一定相关，此类事件更应看它对运营组、项目节奏的影响。
-2. 关键处理缺口：泄露的系统性损害在于宣发节奏失效
-单次泄露的直接损失有限，但持续的内鬼环境会让玩家习惯依赖泄露信息做抽卡决策——尤其3.X纯五星卡池环境下，玩家“看内鬼定抽取计划”已成常态。这会系统性削弱官方信息渠道的价值和卡池预热的节奏控制权。
-3. 玩家侧原因：玩家与泄露信息的共生关系
-部分玩家一边反对内鬼一边消费内鬼信息，官方打击行动因此得不到一致的舆论支持，甚至出现“官方信用不足才让内鬼有市场”的反向叙事。</t>
+          <t>1. 3.2上线前约一个月，海外玩家在Discord直播未公开的遐蝶实机内容，超1.2万人观看。
+2. 2025年6月6日，Cognosphere在加州联邦法院起诉，索赔15万美元，事件被国内外媒体广泛报道。
+3. 泄露提前锚定玩家抽取预期，官方前瞻与PV的信息价值被稀释。</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-诉讼进入司法程序，米哈游持续以法律手段打击泄密。泄露本身未随单案收束，内鬼治理是长期工程。
-2. 运营启示
-第一，泄密事件的处理重点是威慑与信息渠道收束，而非单案索赔金额；法律行动本身也是舆情事件，需要配套传播口径，避免被塑造成“大厂欺压玩家”。
-第二，运营侧需评估“玩家已被泄露内容锚定预期”对官宣节奏的影响：泄露发生后，前瞻和PV的信息编排是否需要调整。
-第三，压缩测试内容分发范围、加强构建水印溯源，把泄露定位从“抓人”前移到“源头收束”。</t>
+          <t>1. 根因推断：测试构建的外部分发范围（测试者、代理、合作方）存在管控失效环节。
+2. 此类事件的严重度看它对运营组和项目节奏的影响，与玩家舆情量级不直接相关：持续泄露让玩家依赖内鬼信息定抽卡计划，官方失去卡池预热的节奏控制权。
+3. 舆情侧：出现同情被告与支持维权两种声音，打击行动得不到一致舆论支持。</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>游侠网：米哈游再出手打内鬼，崩铁直播泄秘遭索赔15万美元 ali213.net/news/html/2025-6/939871.html；知乎：让米哈游“崩坏”的内鬼是一群什么人 zhuanlan.zhihu.com/p/689407615</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="400" customHeight="1">
+          <t>1. 处理重点是威慑与源头收束，法律行动本身也是舆情事件，需配套传播口径。
+2. 泄露发生后，运营侧评估官宣节奏是否需要调整（前瞻、PV信息编排）。
+3. 压缩测试分发范围、构建水印溯源，把治理从"抓人"前移到"源头收束"。</t>
+        </is>
+      </c>
+      <c r="I9" s="3" t="inlineStr">
+        <is>
+          <t>游侠网 ali213.net/news/html/2025-6/939871.html；知乎 zhuanlan.zhihu.com/p/689407615</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="210" customHeight="1">
       <c r="A10" s="3" t="inlineStr">
         <is>
           <t>3.4</t>
@@ -964,50 +956,45 @@
           <t>对话跳过 / 剧情梗概功能争议</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>舆情危机</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>1. 功能官宣：开发者电台释放信息
-3.4版本前的开发者电台宣布将实装“对话跳过”与“剧情梗概”功能，未来还将推出“剧情回顾”。消息一出社区迅速升温，B站相关公告评论数达5.6万条，成为当期社区最热话题。
-2. 舆论分裂：支持与反对同时爆发
-支持方认为功能回应了3.X主线冗长的真实痛点，希望快速进入战斗和玩法；反对方担心新玩家跳过剧情后变成“云剧情”玩家、错过社区津津乐道的名场面，破坏以叙事为核心的社区讨论氛围，甚至将其解读为“官方对剧情价值的自我否定”。
-3. 边界澄清：官方明确跳过范围
-官方说明“对话跳过”仅适用于站桩对话，重要剧情节点与演出不可一键跳过。边界明确后，恐慌性解读逐步降温。
-4. 造成影响
-事件不涉及任何服务中断或付费损失，是一次纯粹的功能定位争议；但其讨论量级说明它触碰了玩家对“星铁是什么游戏”的核心认同。</t>
-        </is>
-      </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：功能回应真实痛点，但触碰核心价值认同
-跳过功能本身是对3.X“单版本主线7-8小时”负反馈的正面回应，方向没有问题。争议的根源在于星铁玩家群体中相当一部分人把“重剧情”视为游戏的身份标签，任何弱化剧情地位的信号都会被放大解读。
-2. 关键处理缺口：首次披露时边界信息不足
-最初的官宣没有把“哪些能跳、哪些不能跳”讲透，给了“以后剧情都能跳=剧情不重要了”的恐慌解读空间。边界信息后置，等于让争议先跑了一段。
-3. 玩家侧原因：争的不是按钮，而是官方态度
-支持方和反对方对功能本身的分歧其实有限（跳过站桩对话争议很小），真正的对立在于双方都把功能当作官方对剧情地位的表态来解读。这类价值观分歧型舆情无法靠补偿解决，只能靠精确的信息披露收束。</t>
+          <t>1. 开发者电台宣布3.4实装"对话跳过""剧情梗概"，B站公告评论达5.6万条。
+2. 支持方盼快速进入玩法；反对方担心新玩家"云剧情"、破坏叙事社区氛围，并将功能解读为官方看轻剧情地位。
+3. 官方澄清跳过仅适用于站桩对话、关键演出不可跳，恐慌解读降温；功能上线后未起第二轮争议。</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-功能随3.4正常上线，实际体验中“仅跳过站桩对话”的设计没有引发第二轮争议，讨论热度随版本推进自然消退。事件整体是一次“官宣期争议大于上线后争议”的案例。
-2. 运营启示
-第一，涉及核心体验定位的功能，官宣时要先划清边界、给出设计理念说明，把“不会改变什么”和“会改变什么”同时讲清楚。
-第二，价值观分歧型舆情的处理重点是信息精确度而非态度安抚，模糊表述只会让双方各自向最坏方向解读。
-第三，此类功能的舆情其实是玩家对更深层问题（主线冗长）的情绪出口，运营要识别争议背后的真实痛点并在结构层面回应。</t>
+          <t>1. 根因推断：功能回应了3.X主线冗长的真实痛点，但触碰了玩家"星铁以剧情为核心"的身份认同。
+2. 处理缺口：首次披露未讲清跳过边界，给了"以后剧情都能跳"的解读空间，争议先跑了一段。
+3. 玩家侧：双方对按钮本身分歧有限，争的是官方对剧情价值的态度。</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>腾讯新闻/游民星空：一个“对话跳过”功能怎就让星铁社区炸了锅 news.qq.com/rain/a/20250619A05T5B00；知乎：如何评价3.4开发者电台剧情跳过 zhihu.com/question/1917919097129268527</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="400" customHeight="1">
+          <t>【建议移交玩家运营深入分析；版本运营切入点在内审】
+1. 官宣物料内审：涉及核心体验定位的功能，披露时同步讲清边界与设计理念，"会改什么、不会改什么"一次说完。
+2. 价值观分歧型舆情靠信息精确度收束，补偿和道歉无效。
+3. 争议背后是主线冗长的存量情绪，需在内容结构层面回应。</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>腾讯新闻 news.qq.com/rain/a/20250619A05T5B00；知乎 zhihu.com/question/1917919097129268527</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="210" customHeight="1">
       <c r="A11" s="3" t="inlineStr">
         <is>
           <t>3.7</t>
@@ -1023,50 +1010,44 @@
           <t>昔涟累充武器外观争议</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>舆情危机</t>
+        </is>
+      </c>
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="E11" s="3" t="inlineStr">
-        <is>
-          <t>1. 商业化新品类首发：全服首个武器外观
-3.7版本推出崩铁首个武器（光锥）外观——昔涟专属光锥皮肤“∞的誓约”，特效与动态光影质量较高。获取方式绑定累计充值20000古老梦华：无首充双倍约需1600元，有双倍也需约1006元。
-2. 舆情发酵：“吃相难看”批评集中出现
-知乎、TapTap等平台出现大量批评，认为高额累充门槛是“强行逼氪”，月卡党与零氪党被完全排除在外。知乎相关问题“如何看待3.7版本累计充值1600元赠送昔涟的武器外观”讨论热烈。
-3. 情绪叠加：成为翁法罗斯篇积累不满的出口
-批评并不只针对皮肤本身——玩家对翁法罗斯全篇的剧情节奏、文案风格及此前版本运营积累的不满，在这个商业化动作上集中释放。皮肤只是恰到好处的导火索。
-4. 造成影响
-也有玩家认可全服首款武器皮肤的收藏价值，舆论并非一边倒；事件未涉及服务中断，最终停留在商业化口碑消耗层面，未升级为危机。</t>
-        </is>
-      </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：情感价值拆分售卖触碰商业化边界
-武器外观属于纯情感向内容，把它与高额累充直接绑定，等于把“喜欢角色”这件事拆分成多重付费门槛。玩家可以接受为喜欢付费，但“不充1600就不配拥有角色的完整表达”的感受会触发被排除感。
-2. 关键处理缺口：新品类试水的时机选择失当
-首个武器外观的定价与形式本身就是一次市场试探，选择在玩家对版本整体不满尚未消化的3.7节点、以最高门槛的累充形式推出，等于在情绪水位最高的时候做最激进的商业化实验。
-3. 玩家侧原因：门槛设计制造了群体割裂
-高门槛累充天然把玩家分成“够得着”和“够不着”两群，后者的不满不是“皮肤贵”，而是“官方眼里只有大R”。叠加当期社区情绪，被排除感被进一步放大。</t>
+          <t>1. 3.7推出全服首个武器外观"∞的誓约"，绑定累计充值2万古老梦华（无双倍约1600元）。
+2. 知乎、TapTap集中出现"吃相难看""逼氪"批评，月卡与零氪玩家感到被排除。
+3. 批评夹带翁法罗斯全篇积累的不满，皮肤成为集中释放的出口；也有玩家认可首个武器皮肤的收藏价值，舆论未一边倒。</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-事件停留在争议层面，皮肤照常上线。它为后续外观类商业化提供了明确的市场反馈：品类本身被接受，门槛形式被抵触。
-2. 运营启示
-第一，商业化新品类（外观、皮肤）首发的定价和获取形式要考虑当期社区情绪水位，情绪高位时应选择更保守的方案。
-第二，情感向内容的售卖要谨慎设计分层：低门槛保证“人人可得基础表达”，高门槛承载增值收藏价值，避免全有全无式门槛。
-第三，慢性不满会寻找单点出口，商业化动作最容易成为那个出口；上线前的舆情评估要把“社区当前欠了多少账”算进去，而不是孤立评估单个商品。</t>
+          <t>1. 根因推断：情感向内容与高额累充直接绑定，"喜欢角色"被拆成付费门槛；首个外观品类选择在社区情绪高位、以最高门槛形式试水，商业化方案内审未把当期情绪水位纳入评估。
+2. 玩家侧：高门槛把玩家分成够得着与够不着两群，后者的不满指向"官方眼里只有大R"。</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>知乎：如何看待3.7版本累计充值1600元赠送昔涟的武器外观 zhihu.com/question/1965161355117072810；TapTap：崩铁3.7新皮美则美矣氪度惊人 taptap.cn/moment/731988471983375369</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="400" customHeight="1">
+          <t>【建议移交玩家运营深入分析；版本运营切入点在内审】
+1. 商业化方案内审：新品类首发的定价与获取形式，叠加当期社区情绪水位评估，情绪高位选保守方案。
+2. 情感向内容做分层：低门槛保证基础表达人人可得，高门槛承载增值收藏。
+3. 慢性不满会找单点出口，商业化动作最易成为出口，上线前把"社区当前欠的账"算进风险评估。</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t>知乎 zhihu.com/question/1965161355117072810；TapTap taptap.cn/moment/731988471983375369</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="210" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
@@ -1082,50 +1063,44 @@
           <t>虚构叙事关卡校验失败</t>
         </is>
       </c>
-      <c r="D12" s="5" t="inlineStr">
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>严重</t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t>1. 期数轮换：新一期虚构叙事上线
-2026年1月5日，虚构叙事「史诗集群」新一期开放。虚构叙事是每期轮换的深渊类挑战玩法，与固定星琼奖励挂钩，玩家通常在开放初期集中挑战满星。
-2. 异常表现：其四击败BOSS后无法结算
-玩家在其四击败上半BOSS后出现“关卡校验失败(2002)”报错，无法完成结算，确认后退回编队界面，且已使用的秘技点被消耗。挑战成果作废，玩家无法通过正常游玩获取该期奖励。
-3. 玩家感知：有损失但情绪偏调侃
-问题边界清晰（特定关卡、特定报错码），玩家判断“是官方的bug、修了就好”，社区反馈集中但情绪不激烈，评论区以玩梗索要“1600星琼”补偿为主。
-4. 造成影响
-影响的是每期固定奖励的获取进度和挑战体验，属于标准的线上技术事故；官方按惯例定位修复并补偿，事件未发酵。</t>
-        </is>
-      </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：轮换配置与战斗结算校验不一致
-虚构叙事每期更换敌方阵容、增益机制和关卡配置，结算时服务端会对战斗数据做校验。特定敌方组合或机制触发了校验逻辑与实际战斗数据的不一致，导致合法战斗被判定为校验失败。
-2. 关键处理缺口：轮换期数的上线前回归测试
-每期新配置实质上是一次“小版更”，但测试强度往往低于正式版更。边界情况（特定BOSS、特定机制交互）的结算校验没有被覆盖到。
-3. 玩家侧原因：损失明确但可等待，焦虑低于限时/付费类事故
-奖励是固定的、期内可补，玩家知道修复后可以重打，因此没有“错过即损失”的时间压力。这解释了为什么同为“严重”级事故，它的舆情烈度远低于支付或资格类问题。</t>
+          <t>1. 2026年1月5日「史诗集群」其四，玩家击败上半BOSS后报"关卡校验失败(2002)"，无法结算，退回编队界面且秘技点已消耗。
+2. 问题边界清晰，社区反馈集中但情绪偏调侃，评论区以玩梗索要补偿为主。
+3. 官方定位修复并按惯例补偿。</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-官方定位修复，并按惯例对受影响玩家补偿（含秘技点等隐性消耗的覆盖）。事件作为标准技术事故平稳收束，是“官方响应和补偿有惯例可循”的正面样本。
-2. 运营启示
-第一，轮换类玩法每期新配置都应视为一次小版更做回归测试，重点覆盖新机制与结算校验的交互。
-第二，补偿要覆盖隐性消耗（秘技点、消耗品、时间成本），只补星琼会留下“官方没算清我的损失”的尾巴。
-第三，这类事故说明玩家对技术故障本身的容忍度其实很高——只要响应快、口径清楚、补偿到位，事故甚至能以社区玩梗的方式软着陆。真正消耗信任的从来不是bug本身，而是处理方式。</t>
+          <t>1. 根因推断：虚构叙事每期轮换敌方与机制配置，特定组合触发结算校验与战斗数据不一致，合法战斗被误判。
+2. 处理缺口：轮换期数实质是一次小版更，测试强度低于正式版更，边界情况未覆盖。
+3. 玩家侧：奖励固定、期内可补打，无"错过即损失"的时间压力，舆情烈度低于支付、资格类事故。</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>知乎：如何看待1月5日虚构叙事「史诗集群」其四bug无法结算 zhihu.com/question/1991395299567101176</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="400" customHeight="1">
+          <t>1. 启示：轮换玩法每期新配置按小版更做回归测试，重点覆盖新机制与结算校验的交互。
+2. 补偿覆盖秘技点等隐性消耗，只补星琼会留尾巴。
+3. 玩家对技术故障容忍度较高，响应快、口径清、补偿到位即可软着陆，可让板块二不全是舆情。</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>知乎 zhihu.com/question/1991395299567101176</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="210" customHeight="1">
       <c r="A13" s="3" t="inlineStr">
         <is>
           <t>3.X</t>
@@ -1138,53 +1113,47 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>3.0翁法罗斯主线冗长 + 老角色保值危机</t>
-        </is>
-      </c>
-      <c r="D13" s="7" t="inlineStr">
+          <t>翁法罗斯主线冗长 + 老角色保值危机</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>舆情危机</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
         <is>
           <t>中等</t>
         </is>
       </c>
-      <c r="E13" s="3" t="inlineStr">
-        <is>
-          <t>1. 结构变化：3.0起版本内容形态调整
-3.0进入翁法罗斯篇后，单版本主线体量增至7-8小时，同时删减了此前版本常见的配音长活动和支线内容。“主线冗长”“流水账”的批评从3.0开篇持续到3.7收尾。
-2. 数值焦虑并行：老角色保值危机发酵
-3.X新角色数值持续抬升，1.X-2.X老角色缺乏加强手段，卡池阵容转向纯五星、无四星新角色，小额付费玩家被迫“抽强度而非抽喜欢”。“老角色贬值”“数值膨胀”成为与剧情批评并行的长期议题。
-3. 慢性积累：不满在多个单点事件上反复引爆
-这不是单点事故，而是贯穿3.X的慢性舆情。它先后借银河幸运星文案争议、昔涟皮肤累充、3.7收尾剧情不满等单点事件集中释放，每次爆发的能量都包含此前积累的存量情绪。
-4. 造成影响
-版本口碑与玩家留存承压，社区“对比2.X贬低3.X”成为常态叙事；官方后续以老角色加强、跳过功能、体验优化等结构性动作回应。</t>
-        </is>
-      </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：内容策略与玩家时间成本、付费保值预期双重错位
-大体量强制主线假设玩家愿意投入整块时间，与长线运营期玩家的实际时间预算冲突；纯五星卡池+数值抬升则动摇了“已付费资产长期有效”的预期。两条线共同指向同一种感受：跟上版本的成本越来越高。
-2. 关键处理缺口：缺少慢性舆情的监控与分版本缓释
-突发事故有明确的响应流程，慢性不满没有。“情绪水位”缺少定期评估，缓解措施（老角色加强、跳过功能）出台滞后，等到单点事件引爆时，处理的就不只是当次问题，还有全部存量情绪。
-3. 玩家侧原因：时间负担与资产贬值感叠加
-玩家的核心感受是“游戏在要求我付出更多（时间、金钱），但我已有的投入在贬值”。这种感受不会立即导致流失，但会持续降低对任何单次失误的容忍度。</t>
+          <t>1. 3.0起单版本主线增至7-8小时并删减配音活动，"冗长""流水账"批评贯穿3.X。
+2. 同期新角色数值抬升、老角色缺乏加强、卡池转向纯五星，"老角色贬值"焦虑并行发酵。
+3. 属慢性积累型舆情，先后借银河幸运星文案、昔涟皮肤、3.7收尾剧情等单点事件集中引爆。</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-官方陆续推出对话跳过/剧情梗概功能、老角色加强等结构性回应，方向正确但时机滞后——多数措施是在不满已经借单点事件爆发后才落地的。
-2. 运营启示
-第一，慢性舆情需要与突发事故不同的监控体系：版本留存、长草期社区情绪、对比性叙事（“2.X比3.X好”）的出现频率都是先行指标。
-第二，结构性问题只能用结构性方案回应（功能、数值、内容形态调整），单次补偿无效；且方案出台越早，成本越低。
-第三，评估任何单点事件的舆情风险时，必须把存量情绪算进去——同一个失误在情绪水位高低不同的时期，后果可能相差一个量级。这是把板块二各案例串起来看的关键视角。</t>
+          <t>1. 根因推断：大体量强制主线与玩家时间预算冲突，数值膨胀动摇"已付费资产长期有效"预期，两条线共同指向"跟上版本的成本越来越高"。
+2. 处理缺口：慢性不满缺少监控指标与分版本缓释，缓解措施（老角色加强、跳过功能）出台滞后，单点引爆时要一并偿还存量情绪。</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>腾讯新闻：备受期待的星铁翁法罗斯为什么会出现争议 news.qq.com/rain/a/20250120A06VF800；知乎：翁法罗斯篇3.7收尾整体评价 zhihu.com/question/1969690484126521334；TapTap：翁法罗斯引发争议 taptap.cn/moment/742721387327655131</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="400" customHeight="1">
+          <t>【建议移交玩家运营深入分析；版本运营配合内容结构决策】
+1. 慢性舆情建监控指标：版本留存、长草期情绪、"2.X比3.X好"对比叙事的出现频率。
+2. 结构性问题用结构性方案回应（功能、数值、内容形态），单次补偿无效，出台越早成本越低。
+3. 评估任何单点事件时把存量情绪算入——这是把板块二各案例串起来看的关键视角。</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>腾讯新闻 news.qq.com/rain/a/20250120A06VF800；知乎 zhihu.com/question/1969690484126521334</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="210" customHeight="1">
       <c r="A14" s="3" t="inlineStr">
         <is>
           <t>1.6-2.0</t>
@@ -1192,58 +1161,51 @@
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>2024/08（报道）</t>
+          <t>2024/08报道</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>测试人员8次进入机房偷录偷摄并向第三人披露</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="inlineStr">
+          <t>测试人员8次进入机房偷录并向第三人披露</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="inlineStr">
+        <is>
+          <t>内控泄密</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>一般</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
-        <is>
-          <t>1. 泄露发生：受控测试环境被突破
-陈某先后8次前往指定游戏测试机房参与测试，期间违反保密协议偷录、偷摄测试内容，并多次向第三人披露。泄露横跨1.6-2.0多个版本的未公开内容。
-2. 司法追责：进入法律程序并被媒体报道
-米哈游追责，案件进入司法程序，2024年8月经腾讯新闻等媒体报道进入公众视野，成为米哈游系统性打击内鬼的又一案例。
-3. 玩家感知：围观新闻，无直接体验影响
-事件对玩家侧无任何服务影响，多数玩家将其当作新闻围观，讨论集中在米哈游维权力度、内鬼产业链和“测试都能偷拍”的管控话题上。
-4. 造成影响
-未公开内容提前扩散，影响相关版本的官宣节奏；线下受控测试的保密公信力受损。此类事件的严重性应按“对运营组和项目的影响”评估，而非玩家舆情量级。</t>
-        </is>
-      </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：物理管控与人员筛选双重失效
-线下机房本是管控最严的测试形态，仍被手机偷拍突破且重复发生8次，说明设备管控（进场检查、录制检测）和过程监督都存在缺口；同一人多次得手也说明异常行为没有被及时识别。
-2. 关键处理缺口：泄露发现与响应的滞后
-从多次偷录到司法追责之间存在时间差，期间泄露内容已完成扩散。对运营而言，泄露被发现时损害已经发生，事后追责无法回收信息。
-3. 玩家/舆情侧特点：损害主体是项目而非玩家
-与影响玩家体验的事故不同，本案的“受害方”是项目的内容节奏和保密体系。玩家甚至可能是泄露信息的消费者，这决定了它的舆情形态是围观而非抗议。</t>
+          <t>1. 陈某先后8次前往指定测试机房参与测试，违反保密协议偷录偷摄，多次向第三人披露，泄露横跨多个版本的未公开内容。
+2. 米哈游追责，案件进入司法程序，2024年8月经媒体报道。
+3. 玩家侧无服务影响，讨论集中在维权力度与内鬼产业链。</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-案件进入司法程序，与遐蝶泄露诉讼等共同构成米哈游全球打击内鬼的案例序列。泄露治理是长期工程，单案判决的价值主要在威慑。
-2. 运营启示
-第一，线下测试的物理防泄露要配套到位：进场设备管控、屏幕水印溯源、录制行为检测，让“偷拍可行”本身不成立。
-第二，建立泄露分级响应机制：泄露发生后第一时间评估泄露内容是否波及当期卡池、官宣物料，决定是否调整披露节奏，而不是只走法务线。
-第三，泄露事件的严重度评估维度与常规事故不同——看它消耗了多少项目的节奏控制权和保密公信力，此类案例应作为运营侧迭代保密流程的输入。</t>
+          <t>1. 根因推断：线下机房是管控最严的测试形态，仍被手机偷拍突破且重复8次，说明进场设备管控、录制检测与过程监督均有缺口，异常行为未被及时识别。
+2. 泄露被发现时扩散已完成，事后追责无法回收信息；损害主体是项目的内容节奏与保密公信力，玩家甚至是泄露信息的消费者，舆情形态为围观而非抗议。</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t>腾讯新闻：陈某测试机房偷录案报道 news.qq.com/rain/a/20240808A08UYO00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="400" customHeight="1">
+          <t>1. 物理防泄露配套到位：进场设备管控、水印溯源、录制行为检测。
+2. 建立泄露分级响应：先评估泄露内容是否波及当期卡池与官宣物料、是否调整披露节奏，再走法务线。
+3. 此类事件按"对运营组和项目的影响"定级，可作为保密流程迭代的输入。</t>
+        </is>
+      </c>
+      <c r="I14" s="3" t="inlineStr">
+        <is>
+          <t>腾讯新闻 news.qq.com/rain/a/20240808A08UYO00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="210" customHeight="1">
       <c r="A15" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
@@ -1261,51 +1223,150 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
+          <t>技术事故</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
           <t>致命</t>
         </is>
       </c>
-      <c r="E15" s="3" t="inlineStr">
-        <is>
-          <t>1. 活动上线：三周年「星穹贺礼」H5承载实体福利
-4.2三周年期间，「星穹贺礼」网页活动分“贺礼任务”“幸运抽奖”“好友互助”三阶段发放240万份实体纪念册。贺礼任务阶段窗口极短（4月22日-4月26日3:59），完成6项任务可直接获得纪念册，未完成的任务转化为抽奖阶段的抽奖机会。
-2. 异常表现：H5页面任务进度被重置
-部分玩家反馈活动页面进度被重置/清零，已完成的任务状态丢失。对玩家来说，进度直接对应免费纪念册资格与抽奖次数，重置等于资格受威胁。
-3. 玩家感知：短窗口下的资格恐慌
-任务窗口只有约4天，进度清零后玩家不确定还来不来得及重新完成、重做后能否被正确记录、最终资格以哪次状态为准。与同期纪念册登录时间异常（见经典案例）叠加，玩家对整个周年资格体系的信任被反复冲击。
-4. 造成影响
-事故直接命中“关键奖励资格”，且发生在三周年这一情绪高点，属于致命级：玩家不可自救、涉及限量实体福利、时间窗口极短。</t>
-        </is>
-      </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：H5进度存储与账号状态同步异常
-网页活动的进度通常涉及前端缓存、账号登录态、服务端进度回写多个环节。跨端登录、登录态失效、接口回写失败或版本发布覆盖数据，都可能表现为玩家侧“进度被重置”。三周年H5并发量级大，同步链路在峰值下最容易出现不一致。
-2. 关键处理缺口：短窗口+实体限量奖励的活动缺少进度强一致与可恢复保障
-普通H5进度丢了可以重做，但贺礼任务窗口只有4天且直接决定实体资格，这类活动的进度数据必须做到服务端留档、可恢复、可申诉，并预留异常缓冲期。缺少这些保障，任何技术抖动都会直接转化为资格损失。
-3. 玩家侧原因：实体纪念册不可补发+窗口极短，焦虑强度最高
-与线上奖励不同，实体纪念册限量、分批、先到先得，玩家默认错过难补。进度重置恰好命中“我可能因为官方的bug失去资格”这一最强不满模型，公平性质疑（我重做来不及、别人没遇到bug）会迅速出现。</t>
+          <t>1. 「星穹贺礼」H5分贺礼任务、幸运抽奖、好友互助三阶段发放240万份实体纪念册；贺礼任务窗口仅4月22日-26日，完成6项任务可直接获得纪念册，未完成任务转化为抽奖机会。
+2. 部分玩家页面进度被重置，已完成任务状态丢失，直接威胁纪念册资格与抽奖次数。
+3. 窗口极短，玩家不确定重做是否来得及、能否被正确记录、资格以哪次为准；与纪念册登录时间异常叠加，周年资格体系信任被反复冲击。</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1. 后续落地
-此类问题的落地关键在于官方能否快速回答三个问题：进度能否恢复、资格是否受影响、窗口是否顺延。对短窗口资格类活动，恢复进度和延长窗口比任何补偿都更对症。
-2. 运营启示
-第一，涉及实体资格的H5活动，进度必须服务端留档并具备恢复能力，前端展示只能作为查询视图而非资格依据。
-第二，短窗口任务设计本身要预留异常缓冲：窗口长度要考虑“出一次事故后玩家还来得及重做”的余量，或明确异常时自动顺延的规则。
-第三，异常发生后第一时间公告“进度是否可恢复、资格是否受影响、是否顺延”，直接回应资格焦虑；技术归因可以后置。
-第四，与纪念册登录时间异常合并来看：周年实体福利的资格链路（登录统计、任务进度、领取状态）是同一条信任链，任何一环出问题都会传导到整个活动的公信力，应作为周年版本的最高优先级保障对象。</t>
+          <t>1. 根因推断：H5进度涉及前端缓存、登录态、服务端回写多环节，跨端登录、回写失败或发布覆盖数据都可表现为进度重置；周年级并发下同步链路最易出现不一致。
+2. 处理缺口：短窗口+实体限量的活动，进度数据未做到服务端留档、可恢复、可申诉。
+3. 玩家侧：实体纪念册限量难补发，进度重置命中"因官方bug失去资格"的最强不满模型，公平性质疑随即出现。</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t>米游社：「星穹贺礼」240万份纪念册免费领 miyoushe.com/sr/article/74524421；游民星空：三周年纪念册领取教程 gamersky.com/handbook/202604/2122527.shtml；17173：纪念册领取任务7选6规则分析 news.17173.com/content/04112026/171440996.shtml</t>
+          <t>1. 涉及实体资格的H5，进度必须服务端留档并可恢复，前端展示只作查询视图。
+2. 短窗口任务预留异常缓冲：窗口长度考虑"出一次事故后玩家还来得及重做"，或明确异常自动顺延规则。
+3. 异常后第一时间公告进度能否恢复、资格是否受影响、窗口是否顺延，技术归因后置。
+4. 周年实体福利的资格链路（登录统计、任务进度、领取状态）是同一条信任链，应作为周年版本最高优先级保障对象。</t>
+        </is>
+      </c>
+      <c r="I15" s="3" t="inlineStr">
+        <is>
+          <t>米游社 miyoushe.com/sr/article/74524421；游民星空 gamersky.com/handbook/202604/2122527.shtml；17173 news.17173.com/content/04112026/171440996.shtml</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A1:I1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>1.0 ｜ 景元卡池开启时充值延迟/无法到账 ｜【致命】｜ 2023/05 ｜ 技术事故（登录支付核心链路）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="300" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>事件发生链路与直接影响</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1. 卡池开启：支付订单瞬时到达峰值
+2023年5月17日景元卡池开启。景元是公测后首个高人气限定五星，开池即出现集中充值。
+2. 异常表现：充值延迟超20分钟，部分订单长时间未到账
+玩家支付完成后星琼迟迟不到账，TapTap、微博集中反馈，"被氪爆"成为当日热议话题。故障发生在付费核心链路，且正值抽卡窗口，"钱已扣、货未到"的焦虑被限时卡池放大。
+3. 官方措施：当日修复、补发、补偿三步闭环
+官博当日公告"已注意到充值到账延迟问题，正在修复中"；18:30修复完成；21:15前逐步完成未到账商品补发。未到账玩家用原设备重新登录即自动发放，仍未到账可凭订单截图联系客服。随后以游戏内邮件向玩家发放星琼×120补偿。
+4. 直接影响
+影响时长约数小时，覆盖卡池开启的付费高峰段。由于响应快、补发路径明确、补偿及时，事件当日收束，未升级为信任危机。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="300" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>造成影响的根因推测与玩家侧原因</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1. 根因推断：支付发货链路未按卡池峰值扩容
+开服首个大人气卡池的订单量远超日常水位，支付回调与发货队列在峰值下积压，表现为到账延迟。公测初期缺少同量级历史数据，峰值预估不足。
+2. 关键处理缺口：故障期间的玩家侧口径
+修复完成前，玩家最需要确认"已支付订单不会丢失、会自动补发"。公告若晚于社区发酵，焦虑会先行扩散。本次官方当日给出口径，缺口未被放大。
+3. 玩家侧原因：支付异常的容忍度最低
+限时卡池+抽卡冲动情境下，玩家对到账时效极度敏感；20分钟延迟在其他场景可接受，在"正在抽卡"场景里会被当作服务中断，并直接触发"骗氪"联想。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="300" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>后续落地情况与版本运营启示</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>1. 后续落地
+"修复→补发→补偿"当日完成闭环。此后大型卡池节点的支付稳定性成为版本保障例行项，后续类似节点未再出现同量级支付事故。
+2. 对版本运营的启示
+第一，卡池开启、周年庆等付费峰值节点，支付与发货链路提前扩容并做峰值演练。
+第二，支付类公告先回答玩家关心的三件事：已支付订单是否安全、何时到账、找谁处理；技术原因可以后置。
+第三，"快速修复+自动补发+小额全服补偿"符合积极响应、玩家有利原则，可作为付费类事故的标准处理范式。
+第四，本案是1.x开服期实际发放线上补偿的事故样本：影响约数小时、补偿星琼×120，可作为后续同类事故补偿定标的参考基线。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>参考资料：游民星空 gamersky.com/news/202305/1598070.shtml；每经网 nbd.com.cn/articles/2023-05-17/2829739.html；52pk news.52pk.com/shtml/20230518/7550167.shtml；TapTap官方修复说明 taptap.cn/moment/408008642420281110</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:C1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/候选事故案例简短分析.xlsx
+++ b/候选事故案例简短分析.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="候选案例简短分析" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="景元卡池支付事故·深入分析" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="经典案例修订·星期日与大丽花" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -105,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -143,6 +144,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1370,4 +1374,142 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="68" customWidth="1" min="3" max="3"/>
+    <col width="68" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" t="inlineStr"/>
+      <c r="C1" s="14" t="inlineStr">
+        <is>
+          <t>2.7 ｜ 星期日CG疑似抄袭阴阳师CG，阴阳师官博下场阴阳 ｜【严重】｜ 舆情危机</t>
+        </is>
+      </c>
+      <c r="D1" s="14" t="inlineStr">
+        <is>
+          <t>3.8 ｜ 大丽花 / 康士坦丝角色争议 ｜【严重】｜ 舆情危机</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="330" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
+        <is>
+          <t>①</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>事件发生链路与直接影响</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>1. 争议出现：分镜对比迅速扩散
+2024年12月2日晚至3日，星期日PV「独奏者」发布后，NGA、TapTap、B站、抖音出现与《阴阳师》月读、寻香行CG的对比帖和对比视频，争议集中在水面、跪姿、神像、光影、构图。对方CG发布在先，讨论很快从"风格相似"转向"是否抄袭"。
+2. 竞品下场：事件升级为厂商间公开互动
+12月3日《阴阳师》官博发布"老铁，崩不住了……"，被普遍理解为含蓄回应，传播明显放大，焦点转向厂商原创性与宣发审核。
+3. 法务表态：争议进入版权风险范畴
+阴阳师侧释放法务介入、完成取证、保留追责权利等信息，资讯号获得持续跟进的理由。
+4. 影响
+PV本应服务角色塑造与抽取情绪积累，争议使传播焦点转向"是否抄袭""官方是否回应"，宣发正向效果被削弱。星铁侧无专项回应，外部叙事由竞品和社区主导，"默认""心虚"等解读持续消耗品牌原创性评价。</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>1. 预期形成：等待已久的卫星角色
+康士坦丝以"大丽花"称呼早在官方内容中登场，争议前玩家关注集中在抽取计划、配队与外观期待。
+2. 争议发酵：批评从审美转向真实案件指控
+正式上线前，内鬼曝光建模与星魂光锥后，小红书、微博先出现围绕媚宅、身材的批评；11月6日风向转向"参考真实虐杀女性案件、性化女角色"的指控；11月7日自媒体跟进转发，事件扩散到圈外，有网友向监管部门举报（极目新闻报道）。
+3. 舆论分裂
+11月8日起抖音同时出现两类内容：质疑方将命名、黑色花卉、动作细节关联"黑色大丽花案"；反驳方认为属过度联想、恶意带节奏。
+4. 官方措施与影响
+公开回应停留在客服流程口径（收到反馈、向上反馈、以公告为准），无专项说明。解释空白使事件叙事由截图、考据和短视频二创主导，争议升级为内容伦理与监管投诉风险，直接干扰重点角色预热期的PV传播、卡池预热和品牌内容安全判断。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="330" customHeight="1">
+      <c r="A3" s="11" t="inlineStr">
+        <is>
+          <t>②</t>
+        </is>
+      </c>
+      <c r="B3" s="12" t="inlineStr">
+        <is>
+          <t>造成影响的根因推测与玩家侧原因</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>1. 根因推断：宣发内审缺少竞品比对环节
+水面、神像、跪姿等母题在二游CG中常见，单元素相似难成事故；对比图、对比视频形成直观的"分镜相似"观感后才被引爆。宣发内审更关注PV质量、角色调性和价值观安全，缺少"同赛道竞品已有CG是否存在高传播相似点"的检查。
+2. 处理缺口：风险定级滞后
+竞品官博下场、法务表态出现后，事件性质已变，但未被及时按版权风险单独定级，公开口径收束有限。
+3. 舆情侧：核心玩家体感弱，外部围观放大
+2.7公告7695条评论中"抄袭/阴阳师/月读/法务"无有效命中；TapTap投票"无所谓啦"占40.8%。扩散主体是围观群众、竞品粉丝与资讯号，传播条件齐全：可剪辑的对比图、官博玩梗的冲突感、法务表态的跟进理由、米哈游vs网易的圈层对立。</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>1. 根因推断：内审对组合联想风险识别不足
+单看命名、黑色花卉、暗黑气质，均可归入哥特美学设计；代号、本名、视觉符号、动作台词被组合解读后，才出现指向"黑色大丽花案"的空间。内审通常盯政治、宗教、血腥、低俗等明确红线，对"真实案件/受害者记忆/跨语言命名联想"类组合风险覆盖不够。星铁命名大量使用花卉、神话、文学意象，创作空间越大，越需要预热前反向检索。
+2. 处理缺口：未及早完成风险切分与传播降温
+这是外部议题套入型舆情：正面解释可能被当作承认争议成立，流程化客服口径又接不住已被外部平台定性的高敏议题；恶意拼接与过度联想内容缺少平台侧处理。
+3. 舆情侧：发酵主体并非核心玩家
+推动扩散的是性别议题群体、反米情绪与平台流量；"性感角色+真实命案+未成年人产品+品牌争议"标签叠加成传播框架，后续还出现波及弱相关UP主与品牌的连坐式扩散。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="330" customHeight="1">
+      <c r="A4" s="11" t="inlineStr">
+        <is>
+          <t>③</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>后续落地情况与版本运营启示</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>【舆情危机：建议移交玩家运营深入分析；版本运营切入点在宣发物料内审】
+1. 后续落地
+星铁侧低调处理，2.7与星期日卡池正常上线，热度随版本内容稀释；阴阳师侧凭官博玩梗与法务表态占据外部叙事位置。定级为中等偏严重的宣发风险事件。
+2. 内审启示
+第一，内审加一道竞品比对：重点角色PV发布前，对同赛道竞品高传播CG做快速相似性检查；能被截图并排传播的镜头都是风险点。
+第二，制作过程留档：分镜草稿、参考清单存档，争议发生时可快速判断相似点属常见母题、正常参考还是高风险。版权争议靠证据链，社区解释作用有限。
+第三，升级触发线前置：普通玩家鉴抄可先观察热度；竞品官博发声、法务表态、媒体报道任一出现，即抬升处理层级，宣发、法务、公关、客服统一口径。</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>【舆情危机：建议移交玩家运营深入分析；版本运营切入点在角色内容内审】
+1. 后续落地
+官方未发布专项公告或创作说明，角色按3.8节奏正常上线，讨论逐渐回到机制、配队与剧情。低调处理避免了二次放大，但外部定性未被收束，重点角色预热期的内容安全风险已经暴露。
+2. 内审启示
+第一，高敏联想排查进内审清单：角色名、外号、英文名、立绘、PV动作、台词、道具合并检视，预热前做跨语言反向检索，覆盖真实案件、受害者、性别、宗教、政治联想。
+第二，舆情来源定性先行：先判断是玩家社区反馈还是泛平台议题化传播，两者处理策略不同；外部定性出现后统一客服与社区口径，并推动平台侧处理恶意拼接内容。
+第三，低调上线可以是策略，但要有内部闭环：舆情监控、口径统一、PV评论区观察、上线后复盘同步完成，避免下次被外部平台抢先定性。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="C1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/候选事故案例简短分析.xlsx
+++ b/候选事故案例简短分析.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>景元卡池开启时充值延迟/无法到账</t>
+          <t>景元卡池充值异常</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1288,7 +1288,7 @@
     <row r="1" ht="22" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>1.0 ｜ 景元卡池开启时充值延迟/无法到账 ｜【致命】｜ 2023/05 ｜ 技术事故（登录支付核心链路）</t>
+          <t>1.0 ｜ 景元卡池充值异常 ｜【致命】｜ 2023/05 ｜ 技术事故（登录支付核心链路）</t>
         </is>
       </c>
     </row>
@@ -1305,14 +1305,15 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
-          <t>1. 卡池开启：支付订单瞬时到达峰值
-2023年5月17日景元卡池开启。景元是公测后首个高人气限定五星，开池即出现集中充值。
-2. 异常表现：充值延迟超20分钟，部分订单长时间未到账
-玩家支付完成后星琼迟迟不到账，TapTap、微博集中反馈，"被氪爆"成为当日热议话题。故障发生在付费核心链路，且正值抽卡窗口，"钱已扣、货未到"的焦虑被限时卡池放大。
-3. 官方措施：当日修复、补发、补偿三步闭环
-官博当日公告"已注意到充值到账延迟问题，正在修复中"；18:30修复完成；21:15前逐步完成未到账商品补发。未到账玩家用原设备重新登录即自动发放，仍未到账可凭订单截图联系客服。随后以游戏内邮件向玩家发放星琼×120补偿。
-4. 直接影响
-影响时长约数小时，覆盖卡池开启的付费高峰段。由于响应快、补发路径明确、补偿及时，事件当日收束，未升级为信任危机。</t>
+          <t>1. 卡池开启：景元上线带来充值高峰
+2023 年 5 月 17 日 18:00，1.0 下半「天戈麾斥」活动跃迁开启，限定五星角色景元与限定五星光锥「拂晓之前」进入概率提升。景元是开服后首批高关注限定角色，卡池开启节点天然会带来集中抽卡和充值流量。
+2. 事故发生：部分玩家充值到账延迟
+同日，官方发布“游戏充值问题通知”，称列车组收到反馈，部分开拓者出现充值到账延迟，技术人员正在紧急排查与修复，并会在问题修复后通过游戏内公告和玩家社区公告通知。
+随后官方发布修复说明：2023/05/17 18:00 起，部分开拓者出现充值异常；问题已于 18:30 修复完成；充值异常期间商品未正常到账的玩家，官方已在 21:15 前逐步完成补发。玩家若仍未到账，需要使用充值时设备重新登录，或联系客服并提供充值订单截图。
+3. 官方措施：修复、补发、补偿同步落地
+官方对该事故采取了三步处理：先发布异常通知，说明已进入排查；随后修复充值到账问题并补发未到账商品；最后发放补偿。补偿内容为星琼 120，补偿范围为 2023/05/17 21:15 前，「星穹列车」服、「无名客」服中开拓等级 ≥4 级的玩家，通过游戏内邮件发放。
+4. 造成影响：直接影响付费链路和抽卡体验
+这次事故持续时间不长，但发生节点非常敏感。问题出现在景元卡池开启当晚。对玩家来说，充值到账延迟会直接带来“钱扣了、货没到”的不安感，也可能影响当时的抽卡节奏、重复充值判断和客服咨询压力。</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1330,14 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>1. 根因推断：支付发货链路未按卡池峰值扩容
-开服首个大人气卡池的订单量远超日常水位，支付回调与发货队列在峰值下积压，表现为到账延迟。公测初期缺少同量级历史数据，峰值预估不足。
-2. 关键处理缺口：故障期间的玩家侧口径
-修复完成前，玩家最需要确认"已支付订单不会丢失、会自动补发"。公告若晚于社区发酵，焦虑会先行扩散。本次官方当日给出口径，缺口未被放大。
-3. 玩家侧原因：支付异常的容忍度最低
-限时卡池+抽卡冲动情境下，玩家对到账时效极度敏感；20分钟延迟在其他场景可接受，在"正在抽卡"场景里会被当作服务中断，并直接触发"骗氪"联想。</t>
+          <t>1. 根因推测
+官方公告没有披露具体技术原因，只能基于公开链路做运营层面的推测。事故从 18:00 起出现，18:30 修复完成，正好覆盖景元卡池开启后的首个高峰。问题表现为“充值异常 / 到账延迟”，更像是支付订单、到账发放、商品补发或状态同步链路在高并发下出现延迟。
+从版本运营视角看，这个事故的风险点根因可能是多方面的。从环节看，玩家付款成功、平台回调、游戏侧确认订单、道具到账、异常订单补发、客服查询。任一环节出现延迟，玩家端看到的结果都会是“充值未到账”。
+2. 关键处理点
+这次事故的官方处理相对完整：当晚先发通知，随后明确修复时间、补发时间、玩家自查方式、客服处理方式和补偿范围。18:00 出现问题，18:30 修复，21:15 前逐步完成补发，节奏上没有拖成跨日事故。
+但它也暴露问题，限定角色卡池开启首小时是支付链路最高压的时间段，尤其是开服 1.0 阶段。支付相关出问题，普通玩家很难判断具体原因，焦虑会快速集中到客服和社区。
+3. 风险放大点
+充值到账问题的敏感性高于一般玩法异常。玩法 bug 通常影响体验，充值异常直接影响玩家对付费安全的信任。尤其在卡池刚开启时，玩家充值目的非常明确，一旦到账延迟，会放大焦虑：已经扣款但资源没到账，担心重复充值造成重复扣款。即使实际修复时间只有半小时，玩家感知上也会非常严重。</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1355,13 @@
       <c r="C4" s="3" t="inlineStr">
         <is>
           <t>1. 后续落地
-"修复→补发→补偿"当日完成闭环。此后大型卡池节点的支付稳定性成为版本保障例行项，后续类似节点未再出现同量级支付事故。
-2. 对版本运营的启示
-第一，卡池开启、周年庆等付费峰值节点，支付与发货链路提前扩容并做峰值演练。
-第二，支付类公告先回答玩家关心的三件事：已支付订单是否安全、何时到账、找谁处理；技术原因可以后置。
-第三，"快速修复+自动补发+小额全服补偿"符合积极响应、玩家有利原则，可作为付费类事故的标准处理范式。
-第四，本案是1.x开服期实际发放线上补偿的事故样本：影响约数小时、补偿星琼×120，可作为后续同类事故补偿定标的参考基线。</t>
+该事故后续完成了修复、补发和全服补偿，没有继续扩大成长期舆情。官方邮件补偿“充值延迟到账问题补偿”，星琼 120。
+从结果看，这是一次处理闭环比较完整的线上事故：事故有通知，修复有时间点，未到账商品有补发，玩家自查有路径，最终还有补偿。
+2. 运营启示
+景元充值异常提醒，充值压力大的阶段应当有单独保障。版本上线、卡池切换、热门角色首发、首充重置、礼包上架，都需要提前和支付、服务器、客服、社区同步值守。
+支付链路监控要看玩家端结果，版本侧需要盯紧玩家的相关声音。
+公告口径要把玩家最关心的问题说清楚，景元事件里这些信息都有给出，所以虽然事故等级高，后续收束相对稳。
+补偿策略要遵循玩家有利原则。充值异常影响付费信任，即使影响时间较短，也应该用明确补偿修复信任预期。</t>
         </is>
       </c>
     </row>
